--- a/phase3/output/课程能力覆盖与缺口分析.xlsx
+++ b/phase3/output/课程能力覆盖与缺口分析.xlsx
@@ -9,18 +9,22 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="能力状态统计" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逐项支撑与缺口" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岗位需求证据不足" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知识条目关联情况" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课程有内容但招聘证据不足" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史岗位证据状态非任务" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未见支撑项建议分类" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="修订前后对照" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="知识条目关联情况" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="课程有内容但招聘证据不足" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'能力状态统计'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐项支撑与缺口'!$A$1:$Q$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'岗位需求证据不足'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'知识条目关联情况'!$A$1:$F$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'课程有内容但招聘证据不足'!$A$1:$K$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'说明'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'逐项支撑与缺口'!$A$1:$X$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'历史岗位证据状态非任务'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'未见支撑项建议分类'!$A$1:$X$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'修订前后对照'!$A$1:$O$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'知识条目关联情况'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'课程有内容但招聘证据不足'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'说明'!$A$1:$B$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +494,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>34</v>
@@ -501,7 +505,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1470588235294118</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -516,7 +520,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>34</v>
@@ -527,7 +531,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -625,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:X35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -636,15 +640,22 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -690,45 +701,80 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>岗位需求证据不足</t>
+          <t>课程支撑的具体技术行为</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>课程尚未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>未见支撑建议分类</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>分类理由</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>分类性质</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>完整工作行为复核说明</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>本轮修订理由</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>历史岗位证据状态（非当前任务）</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>来源岗位ID</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>对应任务ID</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>摘要支持候选岗位数（非独立需求频次）</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>涉及疑似原关系ID</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>涉及疑似原关系数</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>已核验招聘原文岗位数</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>统计分母说明</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>人工审核状态</t>
         </is>
@@ -765,35 +811,70 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见可直接对应的采集与来源整理技术任务</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>外部业务数据采集、来源记录及整理产出</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>可讨论来源记录与基础整理案例，是否纳入仍需课程边界论证</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>JOB002;JOB007;JOB013;JOB022</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="n">
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="V2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -830,35 +911,70 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见业务数据接入的明确技术任务；数据库连接不等于数据接入</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>接口或平台接入、接入结果记录</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>接入与接口集成可由数据集成类课程讨论；未核查实际开课或承担情况</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>JOB035</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>T-JOB035-01</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="n">
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="V3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -897,7 +1013,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -907,39 +1023,74 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>按业务场景编写SELECT条件、多表、子查询、分组及视图查询，运行并查看查询结果</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>未明确真实旅游业务口径验证、跨系统取数与岗位现场结果交付；这些边界不作为该项已定义查询行为的已确认扩展</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>JOB001;JOB002;JOB003;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB019;JOB020;JOB025;JOB028;JOB037;JOB038;JOB043;JOB044;JOB045;JOB050</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB003-02;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB013-02;T-JOB019-01;T-JOB020-01;T-JOB025-01;T-JOB028-01;T-JOB037-01;T-JOB038-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB050-01</t>
         </is>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>R1-0003;R1-0009;R1-0014;R1-0019;R1-0031;R1-0034;R1-0038;R1-0040;R1-0046;R1-0049;R1-0056;R1-0065;R1-0089;R1-0093;R1-0113;R1-0122;R1-0150;R1-0165;R1-0168;R1-0171;R1-0188</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="U4" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="V4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -976,35 +1127,70 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见指标口径或数据字典维护的明确任务</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>指标定义、字段含义、计算口径维护及字典记录</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>可讨论字段与指标字典文档，不宣称原标准已规定</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>JOB003;JOB011</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>T-JOB003-02;T-JOB011-02</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="n">
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="V5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="W5" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1053,35 +1239,70 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>用完整性约束检查数据库记录的规则一致性</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>跨来源核对、汇总差异分析及质量问题记录</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>JOB011;JOB033</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>T-JOB011-02;T-JOB033-01</t>
         </is>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="S6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="n">
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="V6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1130,39 +1351,74 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>用条件更新和视图操作维护数据库记录</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>平台业务规则落实、跨系统同步及完整业务维护结果记录</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>JOB004;JOB018;JOB023;JOB039;JOB046</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>T-JOB004-01;T-JOB018-01;T-JOB023-03;T-JOB039-01;T-JOB046-01</t>
         </is>
       </c>
-      <c r="L7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>R1-0020;R1-0083;R1-0106</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="U7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="V7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1199,35 +1455,70 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见会员标签或画像制作任务；E-R设计不能替代画像方法</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>会员业务标签组织、画像含义及结果说明</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>会员画像方法可能涉及用户分析等课程；不是实际课程承担证明</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>JOB001;JOB046</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>T-JOB001-01;T-JOB001-03;T-JOB046-01</t>
         </is>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="S8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="n">
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="V8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1276,35 +1567,70 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>用约束和条件更新支持部分数据规则一致性处理</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>缺失异常识别、格式标准化、清洗过程与结果说明</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t>JOB002;JOB012;JOB013;JOB046;JOB048</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>T-JOB002-02;T-JOB012-01;T-JOB013-01;T-JOB013-03;T-JOB046-01;T-JOB048-01</t>
         </is>
       </c>
-      <c r="L9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="n">
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="V9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1353,39 +1679,74 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>聚合函数与分组统计完成指标计算子环节</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>指标业务定义、用途分析和指标体系结构设计</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>JOB009;JOB010;JOB011;JOB013;JOB043;JOB047</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>T-JOB009-02;T-JOB010-01;T-JOB011-01;T-JOB011-02;T-JOB013-02;T-JOB043-01;T-JOB047-01</t>
         </is>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="S10" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>R1-0044;R1-0047;R1-0050;R1-0052;R1-0062;R1-0162;R1-0175</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="U10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="V10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="W10" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1434,39 +1795,74 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>查询与分组统计形成统计结果</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>持续监测过程、变化或异常标记及业务记录</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>JOB003;JOB004;JOB005;JOB011;JOB014;JOB018;JOB022;JOB023;JOB026;JOB027;JOB030;JOB031;JOB036;JOB038;JOB043;JOB047;JOB048</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>T-JOB003-01;T-JOB004-01;T-JOB005-01;T-JOB005-02;T-JOB011-02;T-JOB014-02;T-JOB018-01;T-JOB022-01;T-JOB023-02;T-JOB026-01;T-JOB027-01;T-JOB030-01;T-JOB031-01;T-JOB036-01;T-JOB038-01;T-JOB043-01;T-JOB047-01;T-JOB048-01</t>
         </is>
       </c>
-      <c r="L11" s="2" t="n">
+      <c r="S11" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>R1-0021;R1-0026;R1-0052;R1-0069;R1-0084;R1-0104;R1-0114;R1-0116;R1-0125;R1-0128;R1-0144;R1-0152;R1-0162;R1-0175</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="U11" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="V11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1515,39 +1911,74 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>查询与汇总提供业务分析所需的部分数据结果</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>围绕旅游经营问题作解释、归因并形成分析成果</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>JOB001;JOB002;JOB004;JOB006;JOB007;JOB008;JOB009;JOB010;JOB012;JOB013;JOB014;JOB015;JOB016;JOB018;JOB019;JOB020;JOB023;JOB028;JOB029;JOB030;JOB031;JOB033;JOB034;JOB035;JOB036;JOB037;JOB038;JOB041;JOB043;JOB044;JOB045;JOB047</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>T-JOB001-02;T-JOB001-04;T-JOB002-03;T-JOB004-01;T-JOB006-01;T-JOB007-01;T-JOB007-03;T-JOB008-01;T-JOB009-02;T-JOB010-02;T-JOB012-01;T-JOB012-03;T-JOB013-02;T-JOB014-02;T-JOB015-01;T-JOB016-02;T-JOB018-01;T-JOB019-01;T-JOB020-01;T-JOB023-01;T-JOB028-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB033-01;T-JOB034-01;T-JOB035-01;T-JOB036-01;T-JOB037-01;T-JOB038-01;T-JOB041-01;T-JOB043-01;T-JOB044-01;T-JOB045-01;T-JOB047-01</t>
         </is>
       </c>
-      <c r="L12" s="2" t="n">
+      <c r="S12" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>R1-0002;R1-0007;R1-0012;R1-0022;R1-0029;R1-0033;R1-0036;R1-0039;R1-0045;R1-0048;R1-0055;R1-0063;R1-0070;R1-0073;R1-0076;R1-0085;R1-0087;R1-0090;R1-0103;R1-0120;R1-0123;R1-0126;R1-0136;R1-0138;R1-0141;R1-0147;R1-0153;R1-0159;R1-0163;R1-0167;R1-0169;R1-0176</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="U12" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="V12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1579,44 +2010,79 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>不能因同有“模型”一词推定支撑；须先核验岗位建模对象。</t>
+          <t>在现有材料范围无法确定分析模型对象，不将E-R设计等同于分析模型；本轮不开展或要求招聘原文核验。</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见明确数据分析模型训练；E-R模型属于数据库结构设计</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>岗位所称分析模型的对象、输入、用途及模型结果仍需招聘原文澄清</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足无法判断</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>既有摘要中的分析模型对象不明确，在当前证据范围无法判断；不新增招聘核验任务。</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>JOB013;JOB048</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>T-JOB013-02;T-JOB048-01</t>
         </is>
       </c>
-      <c r="L13" s="2" t="n">
+      <c r="S13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>R1-0064</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="U13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="V13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1653,35 +2119,70 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见业务预测模型的明确教学技术任务</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>预测对象、模型输入、预测结果及用途说明</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>预测建模可能由分析建模类课程讨论，未证实实际课程设置</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>JOB037</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>T-JOB037-01</t>
         </is>
       </c>
-      <c r="L14" s="2" t="n">
+      <c r="S14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="n">
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="V14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1718,39 +2219,74 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见经营改进建议形成的明确技术任务</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
+          <t>依据分析提出成本收益或运营建议并说明依据</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>经营建议属于业务决策情境，不应强行扩为数据库核心内容</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t>JOB006;JOB009;JOB019;JOB029;JOB030;JOB031;JOB034;JOB040;JOB042;JOB047</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB040-01;T-JOB042-01;T-JOB047-01</t>
         </is>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="S15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>R1-0158</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="U15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="V15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1787,35 +2323,70 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见转化或增长改进行动的明确技术任务</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>执行运营改进行动并记录增长或转化结果</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>增长执行属于旅游业务运营情境，需专业层面讨论</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>JOB015</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>T-JOB015-02</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
+      <c r="S16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="n">
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="V16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="W16" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1852,39 +2423,74 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见报表报告编制规范；查询结果集不等于报表成果</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>报表报告编制、口径来源标注与可检查文档产出</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>可讨论查询结果的基础报表交付，但须审批任务及评价要求</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>JOB002;JOB003;JOB007;JOB014;JOB018;JOB020;JOB022;JOB023;JOB035;JOB037;JOB043;JOB049</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02</t>
         </is>
       </c>
-      <c r="L17" s="2" t="n">
+      <c r="S17" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>R1-0013;R1-0037;R1-0071;R1-0142;R1-0149;R1-0164</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="U17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="V17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1921,35 +2527,70 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见业务可视化看板制作任务；数据库GUI不是业务看板</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>业务指标可视化呈现、看板制作及含义说明</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>业务看板可由可视化类课程讨论，不等于已由其他课程覆盖</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>JOB003;JOB012;JOB013;JOB036;JOB038;JOB048</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01</t>
         </is>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="S18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="n">
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="V18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -1998,39 +2639,74 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>MySQL环境安装配置与连接</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>旅游业务系统的日常维护、配置变更和维护结果记录</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>JOB001;JOB005;JOB008;JOB017;JOB020;JOB021;JOB022;JOB024;JOB025;JOB027;JOB033;JOB035;JOB039;JOB049</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>T-JOB001-03;T-JOB005-01;T-JOB008-02;T-JOB017-01;T-JOB020-01;T-JOB021-01;T-JOB021-02;T-JOB022-01;T-JOB024-01;T-JOB025-01;T-JOB027-01;T-JOB033-01;T-JOB035-01;T-JOB039-01;T-JOB049-01</t>
         </is>
       </c>
-      <c r="L19" s="2" t="n">
+      <c r="S19" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>R1-0005;R1-0025;R1-0041;R1-0077;R1-0092;R1-0094;R1-0096;R1-0100;R1-0107;R1-0110;R1-0137;R1-0143;R1-0157;R1-0182</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="U19" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="V19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2079,39 +2755,74 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>MySQL安装中的环境错误排查与连接问题处理基础</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>其他业务系统故障定位、完整处理过程及结果记录</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>JOB017;JOB024;JOB032</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>T-JOB017-01;T-JOB024-02;T-JOB032-01</t>
         </is>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="S20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>R1-0078;R1-0108;R1-0131</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="U20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="V20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr">
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2130,7 +2841,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>直接支撑</t>
+          <t>部分支撑</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2150,7 +2861,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2160,35 +2871,70 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>MySQL安装连接、视图索引操作及数据库备份恢复的基础操作</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>数据库或数据库应用系统运行维护对象的完整界定、连续工作过程及维护操作结果记录；课标未明确形成完整运维工作产出</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>JOB021;JOB026</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>T-JOB021-01;T-JOB026-01</t>
         </is>
       </c>
-      <c r="L21" s="2" t="n">
+      <c r="S21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="n">
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="2" t="n">
+      <c r="V21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P21" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="inlineStr">
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2207,7 +2953,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>直接支撑</t>
+          <t>部分支撑</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2227,49 +2973,84 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>项目八明确数据库备份基本流程及独立备份实操，对应备份动作与产物。</t>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>岗位备份对象仍待核验；课程直接支撑限数据库备份。</t>
+          <t>仅确认数据库备份技术环节；业务范围及产物记录未明确覆盖，历史岗位证据状态保留。</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>数据库工具或命令的基本备份流程与独立备份实操</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>备份对象的业务范围确认及备份产物记录要求；不能把数据库备份实验扩大为全部业务数据备份工作</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>JOB005;JOB017;JOB025;JOB027;JOB032</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>T-JOB005-03;T-JOB017-01;T-JOB025-01;T-JOB027-01;T-JOB032-01</t>
         </is>
       </c>
-      <c r="L22" s="2" t="n">
+      <c r="S22" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>R1-0027;R1-0079;R1-0118</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="U22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O22" s="2" t="n">
+      <c r="V22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="2" t="inlineStr">
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2288,7 +3069,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>直接支撑</t>
+          <t>部分支撑</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2308,7 +3089,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>项目八明确恢复流程与独立备份恢复任务，对应恢复操作。</t>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2318,39 +3099,74 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>数据库基本恢复流程和备份恢复实操</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>依据具体业务恢复任务确定对象、实施恢复并形成结果记录的完整要求；不能从恢复实验推定完整业务恢复行为</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>JOB017;JOB032</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>T-JOB017-01;T-JOB032-01</t>
         </is>
       </c>
-      <c r="L23" s="2" t="n">
+      <c r="S23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>R1-0079</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="U23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="V23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="2" t="inlineStr">
+      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2385,7 +3201,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>目标层明确权限管理与DCL，但项目内容和独立实操未明确具体授权任务。</t>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2395,39 +3211,74 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>目标层提出权限管理和DCL基础</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
+          <t>访问对象确认、具体权限配置变更与结果记录；未明确对应授权实操</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>JOB005;JOB025;JOB027</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>T-JOB005-03;T-JOB025-01;T-JOB027-01</t>
         </is>
       </c>
-      <c r="L24" s="2" t="n">
+      <c r="S24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>R1-0028;R1-0119</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="U24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="V24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P24" s="2" t="inlineStr">
+      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2462,7 +3313,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>思政段落提及用户权限、加密与审计，但未说明安全检查或审计记录的技术训练及考核。</t>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2472,39 +3323,74 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>思政段落提及用户权限、加密与审计，尚不能确认技术训练</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>安全检查步骤、审计记录核查与问题记录的技术任务和评价要求</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>JOB017</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>T-JOB017-01</t>
         </is>
       </c>
-      <c r="L25" s="2" t="n">
+      <c r="S25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>R1-0080</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="U25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O25" s="2" t="n">
+      <c r="V25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P25" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2523,7 +3409,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>直接支撑</t>
+          <t>部分支撑</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2543,7 +3429,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2553,35 +3439,70 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>索引创建删除与维护、比较有无索引的查询效果</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>围绕具体查询性能问题说明优化操作及优化结果的完整工作产出；课标明确的是索引技术与效果对比，不是所有查询性能优化工作</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>JOB050</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>T-JOB050-01</t>
         </is>
       </c>
-      <c r="L26" s="2" t="n">
+      <c r="S26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="n">
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="2" t="n">
+      <c r="V26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2630,35 +3551,70 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>识别实体联系并完成E-R设计与关系模式转换</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>系统业务场景、功能约束的完整需求梳理及需求记录</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t>JOB016;JOB032;JOB045</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>T-JOB016-01;T-JOB032-01;T-JOB045-01</t>
         </is>
       </c>
-      <c r="L27" s="2" t="n">
+      <c r="S27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="n">
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="2" t="n">
+      <c r="V27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2707,39 +3663,74 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>库表DDL、数据记录操作与查询等应用数据层操作</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>应用功能实现和可运行业务应用成果；未明确程序连接及端到端业务实现</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>JOB049;JOB050</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>T-JOB049-02;T-JOB050-01</t>
         </is>
       </c>
-      <c r="L28" s="2" t="n">
+      <c r="S28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>R1-0184</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="U28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="V28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2776,39 +3767,74 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见业务系统功能测试方法；SQL运行练习不是软件功能测试</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>功能测试对象、测试过程及测试结果记录</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>系统测试可能由软件测试或项目课程讨论，未检查具体课程标准</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
           <t>JOB008;JOB017</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>T-JOB008-02;T-JOB017-01</t>
         </is>
       </c>
-      <c r="L29" s="2" t="n">
+      <c r="S29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>R1-0081</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="U29" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="V29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P29" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2857,39 +3883,74 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>MySQL安装部署及基本连接</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>旅游业务系统上线、升级对象及完整步骤和结果记录</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>JOB008;JOB017;JOB021;JOB032</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>T-JOB008-02;T-JOB017-01;T-JOB021-03;T-JOB032-01</t>
         </is>
       </c>
-      <c r="L30" s="2" t="n">
+      <c r="S30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>R1-0081</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="U30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O30" s="2" t="n">
+      <c r="V30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2926,35 +3987,70 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见游客市场或业务调查任务</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>确定调研问题、执行调查及形成调研记录</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>游客市场调研属于行业业务背景，不以数据库关键词强配</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>JOB007;JOB014;JOB028</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>T-JOB007-02;T-JOB014-01;T-JOB028-01</t>
         </is>
       </c>
-      <c r="L31" s="2" t="n">
+      <c r="S31" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="n">
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="2" t="n">
+      <c r="V31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="W31" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -2995,39 +4091,74 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>素质目标层提出团队协作意识</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
+          <t>跨部门需求沟通、业务数据支持过程及支持结果记录</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>JOB004;JOB012;JOB017;JOB041</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>T-JOB004-01;T-JOB012-02;T-JOB017-01;T-JOB041-01</t>
         </is>
       </c>
-      <c r="L32" s="2" t="n">
+      <c r="S32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>R1-0082</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="U32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="2" t="n">
+      <c r="V32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P32" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -3064,35 +4195,70 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见系统或操作技术说明文档编制要求</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
+          <t>编制和维护技术说明、操作记录或系统文档</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>可讨论数据库操作文档交付，不能反写为现行要求</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
           <t>JOB021</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>T-JOB021-03</t>
         </is>
       </c>
-      <c r="L33" s="2" t="n">
+      <c r="S33" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="n">
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="2" t="n">
+      <c r="V33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -3141,39 +4307,74 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>SQL操作顺序和事务逻辑等操作流程基础</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>数据处理步骤的完整梳理、衔接关系及流程说明产出</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
           <t>JOB001</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>T-JOB001-04</t>
         </is>
       </c>
-      <c r="L34" s="2" t="n">
+      <c r="S34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>R1-0008</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="U34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="O34" s="2" t="n">
+      <c r="V34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
@@ -3210,42 +4411,77 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>全部来源岗位未核验；摘要支持不是招聘原文明示</t>
+          <t>未见游客服务整改任务</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>服务问题记录、整改进度跟踪和处理结果记录</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>游客服务整改属于行业业务流程背景</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
           <t>JOB014</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>T-JOB014-03</t>
         </is>
       </c>
-      <c r="L35" s="2" t="n">
+      <c r="S35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="n">
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="2" t="n">
+      <c r="V35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>待人工审核</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q35"/>
+  <autoFilter ref="A1:X35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3389,6 +4625,4312 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:X15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="36" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>能力ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>能力名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>最终候选匹配状态</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>知识点ID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>实践任务ID</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>课程证据ID</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>课程支撑判断</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>课程标准支撑不足或边界</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>课程支撑的具体技术行为</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>课程尚未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>未见支撑建议分类</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>分类理由</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>分类性质</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>完整工作行为复核说明</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>本轮修订理由</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>历史岗位证据状态（非当前任务）</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>来源岗位ID</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>对应任务ID</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>摘要支持候选岗位数（非独立需求频次）</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>涉及疑似原关系ID</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>涉及疑似原关系数</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>已核验招聘原文岗位数</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>统计分母说明</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>人工审核状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>N111</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>采集与整理业务数据</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据插入是写入记录，不等于外部业务数据采集与来源整理。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>可讨论数据来源与采集记录训练；这是改进建议，非原课标内容。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>未见可直接对应的采集与来源整理技术任务</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>外部业务数据采集、来源记录及整理产出</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>可讨论来源记录与基础整理案例，是否纳入仍需课程边界论证</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>JOB002;JOB007;JOB013;JOB022</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB002-01;T-JOB007-01;T-JOB013-01;T-JOB022-02</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>N112</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>接入业务数据</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>MySQL连接与数据库操作不能直接证明业务数据接入或接口集成训练。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>若课程定位需要，可另行论证数据接入实践；不补写为现行内容。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>未见业务数据接入的明确技术任务；数据库连接不等于数据接入</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>接口或平台接入、接入结果记录</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>接入与接口集成可由数据集成类课程讨论；未核查实际开课或承担情况</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>JOB035</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB035-01</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>N121</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>维护指标口径与数据字典</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>列定义与关系设计不等同于业务指标口径或数据字典维护，未找到对应明确条目。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>可讨论指标字典文档，但须另行审批课程改进方案。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>未见指标口径或数据字典维护的明确任务</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>指标定义、字段含义、计算口径维护及字典记录</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>可讨论字段与指标字典文档，不宣称原标准已规定</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>JOB003;JOB011</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB003-02;T-JOB011-02</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>N124</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>组织会员标签与画像</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>E-R建模为数据结构设计，不能据此确认会员标签与画像业务方法。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>如需旅游案例，可另议会员数据案例；不得虚构现行画像知识点。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>未见会员标签或画像制作任务；E-R设计不能替代画像方法</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>会员业务标签组织、画像含义及结果说明</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>会员画像方法可能涉及用户分析等课程；不是实际课程承担证明</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>JOB001;JOB046</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB001-01;T-JOB001-03;T-JOB046-01</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>N221</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>构建数据分析模型</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据建模指E-R及关系模式，不是岗位中的数据分析模型。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>在现有材料范围无法确定分析模型对象，不将E-R设计等同于分析模型；本轮不开展或要求招聘原文核验。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>未见明确数据分析模型训练；E-R模型属于数据库结构设计</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>岗位所称分析模型的对象、输入、用途及模型结果仍需招聘原文澄清</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>证据不足无法判断</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>既有摘要中的分析模型对象不明确，在当前证据范围无法判断；不新增招聘核验任务。</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>JOB013;JOB048</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB013-02;T-JOB048-01</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>R1-0064</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>N222</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>构建业务预测模型</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未找到预测对象、预测模型或预测结果训练条目。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>预测任务是否超出单课程范围，需专业课程体系层面审议。</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>未见业务预测模型的明确教学技术任务</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>预测对象、模型输入、预测结果及用途说明</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>预测建模可能由分析建模类课程讨论，未证实实际课程设置</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>JOB037</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB037-01</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>N223</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>提出经营改进建议</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>用数据说话和依事实决策的思政表述，不足以确认经营改进建议的技术训练及评价。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>可保留行业背景需求，由研究者判断课程边界。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>未见经营改进建议形成的明确技术任务</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>依据分析提出成本收益或运营建议并说明依据</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>经营建议属于业务决策情境，不应强行扩为数据库核心内容</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>JOB006;JOB009;JOB019;JOB029;JOB030;JOB031;JOB034;JOB040;JOB042;JOB047</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB006-01;T-JOB009-01;T-JOB019-01;T-JOB029-01;T-JOB030-01;T-JOB031-01;T-JOB034-01;T-JOB040-01;T-JOB042-01;T-JOB047-01</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>R1-0158</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>N224</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>实施业务增长改进</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未找到产品转化或用户增长行动及效果评价的明确教学条目。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>按旅游业务背景保留，勿强行加入数据库知识点。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>未见转化或增长改进行动的明确技术任务</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>执行运营改进行动并记录增长或转化结果</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>增长执行属于旅游业务运营情境，需专业层面讨论</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>JOB015</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB015-02</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>N231</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>编制业务统计报表与报告</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>查询结果集与统计汇总不等于报表报告编制，课标未明确报表文档产出规范。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>如拟增加统计报告，应标课程改进建议并明确评价要求。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>未见报表报告编制规范；查询结果集不等于报表成果</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>报表报告编制、口径来源标注与可检查文档产出</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>可讨论查询结果的基础报表交付，但须审批任务及评价要求</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>JOB002;JOB003;JOB007;JOB014;JOB018;JOB020;JOB022;JOB023;JOB035;JOB037;JOB043;JOB049</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB002-03;T-JOB003-02;T-JOB007-03;T-JOB014-02;T-JOB018-01;T-JOB020-01;T-JOB022-02;T-JOB023-02;T-JOB035-01;T-JOB037-01;T-JOB043-01;T-JOB049-02</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>R1-0013;R1-0037;R1-0071;R1-0142;R1-0149;R1-0164</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>N232</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>制作业务可视化看板</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>课标图形化数据库管理工具和E-R绘图，不等于业务可视化看板制作。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>不把工具“可视化”一词作为看板能力的依据。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>未见业务可视化看板制作任务；数据库GUI不是业务看板</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>业务指标可视化呈现、看板制作及含义说明</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>业务看板可由可视化类课程讨论，不等于已由其他课程覆盖</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>JOB003;JOB012;JOB013;JOB036;JOB038;JOB048</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB003-02;T-JOB012-02;T-JOB013-03;T-JOB036-01;T-JOB038-01;T-JOB048-01</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>N421</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>测试业务系统功能</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>查询运行、测试数据表与SQL练习不等同于业务系统功能测试方法及测试记录。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>如拟增加软件测试任务，应独立论证课程适配性。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>未见业务系统功能测试方法；SQL运行练习不是软件功能测试</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>功能测试对象、测试过程及测试结果记录</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>系统测试可能由软件测试或项目课程讨论，未检查具体课程标准</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>JOB008;JOB017</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB008-02;T-JOB017-01</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>R1-0081</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N511</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>开展旅游业务调研</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客、市场或业务调研及调查记录的明确教学任务。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>保留行业背景，勿推断课标已有旅游调研内容。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>未见游客市场或业务调查任务</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>确定调研问题、执行调查及形成调研记录</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>游客市场调研属于行业业务背景，不以数据库关键词强配</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>JOB007;JOB014;JOB028</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB007-02;T-JOB014-01;T-JOB028-01</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>N521</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>编制与维护技术文档</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>E-R图等设计成果不等同于系统或操作技术文档，未找到明确技术说明文档任务。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>若拟增加操作文档，须单列改进建议及评价要求。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>未见系统或操作技术说明文档编制要求</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>编制和维护技术说明、操作记录或系统文档</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>可讨论数据库操作文档交付，不能反写为现行要求</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>JOB021</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB021-03</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>N531</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>跟进游客服务整改</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客服务问题整改、进度跟踪与结果记录的明确课程任务。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>保持行业背景分类，不强配数据库知识点。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>未见游客服务整改任务</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>服务问题记录、整改进度跟踪和处理结果记录</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>游客服务整改属于行业业务流程背景</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>按第二阶段既有可观察行为复核，未修改职业能力定义；本项结论仍为AI辅助研究建议</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>原候选及推断状态保留；不再开展逐条核验，不作为后续阶段前置条件</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>JOB014</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>T-JOB014-03</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>能力状态比例分母为实际三级候选能力数；不按岗位频次加权</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X15"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>能力ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>能力名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>修订前等级</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>修订后等级</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>等级是否变化</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>修订前判断</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>修订后判断</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>课程支撑的具体技术行为</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>课程尚未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>未见支撑建议分类</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>分类理由</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>分类性质</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>修订理由</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>修订前提交</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>审核状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>N111</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>采集与整理业务数据</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据插入是写入记录，不等于外部业务数据采集与来源整理。</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据插入是写入记录，不等于外部业务数据采集与来源整理。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>未见可直接对应的采集与来源整理技术任务</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>外部业务数据采集、来源记录及整理产出</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>可讨论来源记录与基础整理案例，是否纳入仍需课程边界论证</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>N112</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>接入业务数据</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>MySQL连接与数据库操作不能直接证明业务数据接入或接口集成训练。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>MySQL连接与数据库操作不能直接证明业务数据接入或接口集成训练。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>未见业务数据接入的明确技术任务；数据库连接不等于数据接入</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>接口或平台接入、接入结果记录</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>接入与接口集成可由数据集成类课程讨论；未核查实际开课或承担情况</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>N113</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>查询并提取业务数据</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SELECT、条件、多表及视图查询与按业务问题查询提取数据的技术行为对应，课标要求独立完成查询任务。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>按业务场景编写SELECT条件、多表、子查询、分组及视图查询，运行并查看查询结果</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>未明确真实旅游业务口径验证、跨系统取数与岗位现场结果交付；这些边界不作为该项已定义查询行为的已确认扩展</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>课标要求独立完成业务场景复杂查询、运行查询并查看结果，与本项已定义的查询提取并呈现结果行为相符，因此保留直接支撑的研究建议。直接仅限该项查询行为，不含岗位真实性、真实旅游业务迁移或额外跨系统行为的确认。</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>N121</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>维护指标口径与数据字典</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>列定义与关系设计不等同于业务指标口径或数据字典维护，未找到对应明确条目。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>列定义与关系设计不等同于业务指标口径或数据字典维护，未找到对应明确条目。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>未见指标口径或数据字典维护的明确任务</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>指标定义、字段含义、计算口径维护及字典记录</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>可讨论字段与指标字典文档，不宣称原标准已规定</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>N122</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>核对与校验业务数据</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>完整性约束可支撑数据规则校验部分；课标未明确跨来源汇总核对或差异记录工作流程。</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>完整性约束可支撑数据规则校验部分；课标未明确跨来源汇总核对或差异记录工作流程。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>用完整性约束检查数据库记录的规则一致性</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>跨来源核对、汇总差异分析及质量问题记录</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>N123</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>维护与更新业务数据</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>条件更新与视图数据操作支撑记录维护更新；岗位行为中的数据同步和平台业务规则未获完整支撑。</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>条件更新与视图数据操作支撑记录维护更新；岗位行为中的数据同步和平台业务规则未获完整支撑。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>用条件更新和视图操作维护数据库记录</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>平台业务规则落实、跨系统同步及完整业务维护结果记录</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>N124</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>组织会员标签与画像</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>E-R建模为数据结构设计，不能据此确认会员标签与画像业务方法。</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>E-R建模为数据结构设计，不能据此确认会员标签与画像业务方法。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>未见会员标签或画像制作任务；E-R设计不能替代画像方法</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>会员业务标签组织、画像含义及结果说明</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>会员画像方法可能涉及用户分析等课程；不是实际课程承担证明</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>N125</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>清洗与标准化业务数据</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>约束与条件更新为规则一致性提供基础；课标未明确缺失异常处理、格式标准化及清洗说明。</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>约束与条件更新为规则一致性提供基础；课标未明确缺失异常处理、格式标准化及清洗说明。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>用约束和条件更新支持部分数据规则一致性处理</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>缺失异常识别、格式标准化、清洗过程与结果说明</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>N211</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>构建业务指标体系</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>聚合与分组可支撑指标计算环节，但指标定义、业务用途和体系结构未明确教学。</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>聚合与分组可支撑指标计算环节，但指标定义、业务用途和体系结构未明确教学。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>聚合函数与分组统计完成指标计算子环节</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>指标业务定义、用途分析和指标体系结构设计</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>N212</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>统计与监测业务指标</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>分组统计直接支撑统计结果形成；持续指标监测和异常标记机制未见明确实操。</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>分组统计直接支撑统计结果形成；持续指标监测和异常标记机制未见明确实操。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>查询与分组统计形成统计结果</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>持续监测过程、变化或异常标记及业务记录</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>N213</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>分析旅游经营数据</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>SQL汇总为业务分析提供数据基础，但经营解释与业务分析成果的方法不明确。</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SQL汇总为业务分析提供数据基础，但经营解释与业务分析成果的方法不明确。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>查询与汇总提供业务分析所需的部分数据结果</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>围绕旅游经营问题作解释、归因并形成分析成果</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N221</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>构建数据分析模型</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据建模指E-R及关系模式，不是岗位中的数据分析模型。</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>课标的数据建模指E-R及关系模式，不是岗位中的数据分析模型。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>未见明确数据分析模型训练；E-R模型属于数据库结构设计</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>岗位所称分析模型的对象、输入、用途及模型结果仍需招聘原文澄清</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足无法判断</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>既有摘要中的分析模型对象不明确，在当前证据范围无法判断；不新增招聘核验任务。</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>N222</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>构建业务预测模型</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>未找到预测对象、预测模型或预测结果训练条目。</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未找到预测对象、预测模型或预测结果训练条目。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>未见业务预测模型的明确教学技术任务</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>预测对象、模型输入、预测结果及用途说明</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>预测建模可能由分析建模类课程讨论，未证实实际课程设置</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>N223</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>提出经营改进建议</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>用数据说话和依事实决策的思政表述，不足以确认经营改进建议的技术训练及评价。</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>用数据说话和依事实决策的思政表述，不足以确认经营改进建议的技术训练及评价。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>未见经营改进建议形成的明确技术任务</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>依据分析提出成本收益或运营建议并说明依据</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>经营建议属于业务决策情境，不应强行扩为数据库核心内容</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>N224</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>实施业务增长改进</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>未找到产品转化或用户增长行动及效果评价的明确教学条目。</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未找到产品转化或用户增长行动及效果评价的明确教学条目。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>未见转化或增长改进行动的明确技术任务</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>执行运营改进行动并记录增长或转化结果</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>增长执行属于旅游业务运营情境，需专业层面讨论</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>N231</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>编制业务统计报表与报告</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>查询结果集与统计汇总不等于报表报告编制，课标未明确报表文档产出规范。</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>查询结果集与统计汇总不等于报表报告编制，课标未明确报表文档产出规范。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>未见报表报告编制规范；查询结果集不等于报表成果</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>报表报告编制、口径来源标注与可检查文档产出</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>可讨论查询结果的基础报表交付，但须审批任务及评价要求</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>N232</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>制作业务可视化看板</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>课标图形化数据库管理工具和E-R绘图，不等于业务可视化看板制作。</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>课标图形化数据库管理工具和E-R绘图，不等于业务可视化看板制作。</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>未见业务可视化看板制作任务；数据库GUI不是业务看板</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>业务指标可视化呈现、看板制作及含义说明</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>业务看板可由可视化类课程讨论，不等于已由其他课程覆盖</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>N311</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>维护与配置旅游业务系统</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>MySQL环境安装配置提供数据库环境维护基础，但不覆盖票务、CRM、POS等旅游业务系统运维。</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>MySQL环境安装配置提供数据库环境维护基础，但不覆盖票务、CRM、POS等旅游业务系统运维。</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>MySQL环境安装配置与连接</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务系统的日常维护、配置变更和维护结果记录</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>N312</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>排查业务系统故障</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>项目一明确安装错误排查的教学难点，可支撑数据库环境故障处理基础；业务系统故障范围更广。</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>项目一明确安装错误排查的教学难点，可支撑数据库环境故障处理基础；业务系统故障范围更广。</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>MySQL安装中的环境错误排查与连接问题处理基础</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>其他业务系统故障定位、完整处理过程及结果记录</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>N313</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>执行数据库运行维护</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>MySQL环境、视图索引管理及备份恢复构成基本数据库运行维护行为的明确教学与实操。</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>MySQL安装连接、视图索引操作及数据库备份恢复的基础操作</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>数据库或数据库应用系统运行维护对象的完整界定、连续工作过程及维护操作结果记录；课标未明确形成完整运维工作产出</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确基础数据库操作及若干维护技术，但未明确完整运行维护对象界定、工作过程与操作结果记录产出。不能由视图、索引、备份等技术子环节推定完整数据库或数据库应用系统运行维护能力。</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>N321</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>执行业务数据备份</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>项目八明确数据库备份基本流程及独立备份实操，对应备份动作与产物。</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>数据库工具或命令的基本备份流程与独立备份实操</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>备份对象的业务范围确认及备份产物记录要求；不能把数据库备份实验扩大为全部业务数据备份工作</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库备份流程及实操，支撑备份技术环节；未明确业务范围的备份对象确认和备份产物记录，不能扩大为完整业务数据备份工作。</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>N322</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>恢复业务数据</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>项目八明确恢复流程与独立备份恢复任务，对应恢复操作。</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>数据库基本恢复流程和备份恢复实操</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>依据具体业务恢复任务确定对象、实施恢复并形成结果记录的完整要求；不能从恢复实验推定完整业务恢复行为</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确数据库恢复实验，未明确具体业务恢复任务的对象确认及恢复结果记录要求；实验技术环节不等同完整业务数据恢复工作行为。</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>N331</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>配置与维护访问权限</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>目标层明确权限管理与DCL，但项目内容和独立实操未明确具体授权任务。</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>目标层提出权限管理和DCL基础</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>访问对象确认、具体权限配置变更与结果记录；未明确对应授权实操</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>维持部分支撑：可见目标层提及权限与DCL，但缺少访问对象、权限配置变更及结果记录的具体实操落点，不能认定完整访问权限工作行为直接支撑。</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>N332</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>执行系统安全检查与审计</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>思政段落提及用户权限、加密与审计，但未说明安全检查或审计记录的技术训练及考核。</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>思政段落提及用户权限、加密与审计，尚不能确认技术训练</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>安全检查步骤、审计记录核查与问题记录的技术任务和评价要求</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>维持待人工审核：思政层的用户权限、加密与审计提及不能证明安全检查、审计记录核查及问题记录训练；需教师核对完整可见课标与实施资料，未模拟专家确认。</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>N341</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>优化数据库查询性能</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>直接支撑</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>索引操作及有无索引查询效果对比，与基础查询性能优化行为对应。</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>索引创建删除与维护、比较有无索引的查询效果</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>围绕具体查询性能问题说明优化操作及优化结果的完整工作产出；课标明确的是索引技术与效果对比，不是所有查询性能优化工作</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>修订为部分支撑：课标明确索引操作与有无索引效果对比，仅能确认索引优化技术环节；未明确围绕具体查询性能问题说明完整优化操作和结果的工作产出，不能扩成全面查询性能优化。</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>N411</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>梳理业务系统需求</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>业务场景的实体关系识别和模式转换支撑数据需求梳理部分，完整系统功能与约束文档不明确。</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>业务场景的实体关系识别和模式转换支撑数据需求梳理部分，完整系统功能与约束文档不明确。</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>识别实体联系并完成E-R设计与关系模式转换</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>系统业务场景、功能约束的完整需求梳理及需求记录</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>N412</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>开发数据库业务应用</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>库表、数据操作和查询可支撑应用数据层；课标未明确应用程序连接、端到端业务功能开发。</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>库表、数据操作和查询可支撑应用数据层；课标未明确应用程序连接、端到端业务功能开发。</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>库表DDL、数据记录操作与查询等应用数据层操作</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>应用功能实现和可运行业务应用成果；未明确程序连接及端到端业务实现</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>N421</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>测试业务系统功能</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>查询运行、测试数据表与SQL练习不等同于业务系统功能测试方法及测试记录。</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>查询运行、测试数据表与SQL练习不等同于业务系统功能测试方法及测试记录。</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未见业务系统功能测试方法；SQL运行练习不是软件功能测试</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>功能测试对象、测试过程及测试结果记录</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>其他专业课程可能承担</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>系统测试可能由软件测试或项目课程讨论，未检查具体课程标准</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>N422</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>部署与升级业务系统</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>MySQL安装部署支撑环境部署基础，但业务系统上线与升级步骤未明确。</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>MySQL安装部署支撑环境部署基础，但业务系统上线与升级步骤未明确。</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>MySQL安装部署及基本连接</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务系统上线、升级对象及完整步骤和结果记录</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>N511</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>开展旅游业务调研</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客、市场或业务调研及调查记录的明确教学任务。</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客、市场或业务调研及调查记录的明确教学任务。</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未见游客市场或业务调查任务</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>确定调研问题、执行调查及形成调研记录</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>游客市场调研属于行业业务背景，不以数据库关键词强配</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>N512</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>协调业务与数据支持</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>素质目标提出团队协作，但未明确跨部门业务需求沟通与支持结果的实践任务。</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>素质目标提出团队协作，但未明确跨部门业务需求沟通与支持结果的实践任务。</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>素质目标层提出团队协作意识</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>跨部门需求沟通、业务数据支持过程及支持结果记录</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>N521</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>编制与维护技术文档</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>E-R图等设计成果不等同于系统或操作技术文档，未找到明确技术说明文档任务。</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>E-R图等设计成果不等同于系统或操作技术文档，未找到明确技术说明文档任务。</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未见系统或操作技术说明文档编制要求</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>编制和维护技术说明、操作记录或系统文档</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>本课程潜在改进方向</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>可讨论数据库操作文档交付，不能反写为现行要求</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>N522</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>梳理数据处理流程</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>部分支撑</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>SQL操作顺序与事务逻辑可支撑操作流程意识；未明确完整数据处理流程梳理与流程说明文档。</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>SQL操作顺序与事务逻辑可支撑操作流程意识；未明确完整数据处理流程梳理与流程说明文档。</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>SQL操作顺序和事务逻辑等操作流程基础</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>数据处理步骤的完整梳理、衔接关系及流程说明产出</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>不适用（本项非未见明确支撑）</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>仅对未见明确支撑项分类；其余仍说明未覆盖行为</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>N531</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>跟进游客服务整改</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>未见明确支撑</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客服务问题整改、进度跟踪与结果记录的明确课程任务。</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未找到游客服务问题整改、进度跟踪与结果记录的明确课程任务。</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未见游客服务整改任务</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>服务问题记录、整改进度跟踪和处理结果记录</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>旅游业务背景能力</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>游客服务整改属于行业业务流程背景</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>研究建议，非课程标准证明，也非已核实的其他课程承担事实</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>逐项复核后维持原支撑等级，补充具体技术行为与未明确覆盖的工作行为</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2aec6d909ab7b87799c2ce97f4dbdf1f354d2320</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>待人工审核</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4492,7 +10034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4757,7 +10299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4790,7 +10332,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>岗位全部待核验，课程匹配及图谱语义联系全部待人工审核；文本支撑不等同实际培养</t>
+          <t>历史招聘及关系证据状态保留但不再新增核验任务；当前仅课程能力图谱复核，文本支撑不等同实际培养</t>
         </is>
       </c>
     </row>
